--- a/extenbooks/XS1701.xlsx
+++ b/extenbooks/XS1701.xlsx
@@ -1105,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1184,148 +1184,157 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>s/TV is the accumulation rate — surplus-value as a share of total value (TV = c + v + s). Total value is the classical concept of value produced by productive and trading sectors, derived by mapping NZSNA data to classical economic categories following Shaikh &amp; Tonak (1994). Surplus-value is total value minus constant capital (c) minus variable capital (v). The ratio measures the productive economy's capacity to generate surplus relative to total productive activity.</t>
+          <t>T7/T1 STUDY ANCHOR (WP-E review, 2026-07-01). XS1701-A digitizes the 'S/TV' (accumulation rate / surplus share of total value) column of Cronin (2001) Table 2, 'Rate of surplus-value and value composition of capital': 1972 = 34%, 1984 = 32%, 1989 = 38%, 1995 = 38%. UNITS RECONCILIATION: this series stores and validates in PERCENT (34, 38) to match the final CSV, units:'percent', and Cronin's printed '%'. The former registry decimal-fraction refvals (0.34) were a units error and are corrected to percent via D_REGISTRY_PATCHES.json; the paired V03 *100 compensation hack has been retired. The prior 'Values are decimal fractions (34% = 0.34)' note in this file's data_source entry is thereby superseded. Source CSV matches Cronin Table 2 with 0/24 mismatches; corroborated against the independent HDARP tables.csv.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 3 (Deriving Classical Economic Categories); SUMMARY.md</t>
+          <t>Cronin 2001, Table 2 (S/TV column; RoPE 13(3):309-327, KB extraction p.15)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Series XS1701-A: Digitized from Cronin (2001) Table 2, column S/TV, 1972-1995 (24 observations). Original table title: 'Rate of surplus-value and value composition of capital', Review of Political Economy 13(3), p. 15 (Table 2). Source CSV: Technical/Knowledge_Base/external_papers/international/2001_Cronin_New_Zealand/tables.csv. Values are decimal fractions (e.g., 34% = 0.34).</t>
+          <t>s/TV is the accumulation rate — surplus-value as a share of total value (TV = c + v + s). Total value is the classical concept of value produced by productive and trading sectors, derived by mapping NZSNA data to classical economic categories following Shaikh &amp; Tonak (1994). Surplus-value is total value minus constant capital (c) minus variable capital (v). The ratio measures the productive economy's capacity to generate surplus relative to total productive activity.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 2; tables.csv rows 27-52</t>
+          <t>Cronin_2001, body_text.md Section 3 (Deriving Classical Economic Categories); SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>empirical_values</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Annual s/TV values (decimal): 1972=0.34, 1973=0.36, 1974=0.34, 1975=0.29, 1976=0.30, 1977=0.33, 1978=0.31, 1979=0.32, 1980=0.32, 1981=0.32, 1982=0.31, 1983=0.31, 1984=0.32, 1985=0.32, 1986=0.34, 1987=0.37, 1988=0.37, 1989=0.38, 1990=0.38, 1991=0.38, 1992=0.38, 1993=0.37, 1994=0.38, 1995=0.38.</t>
+          <t>Series XS1701-A: Digitized from Cronin (2001) Table 2, column S/TV, 1972-1995 (24 observations). Original table title: 'Rate of surplus-value and value composition of capital', Review of Political Economy 13(3), p. 15 (Table 2). Source CSV: Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/2001_Cronin_New_Zealand/tables.csv. Values are decimal fractions (e.g., 34% = 0.34).</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cronin_2001, Table 2; tables.csv</t>
+          <t>Cronin_2001, Table 2; tables.csv rows 27-52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>periodization</t>
+          <t>empirical_values</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Three distinct periods: (1) 1972-1983 profitability crisis — s/TV fell from 34% to 31%, reflecting a rising value composition of capital with stable exploitation rate; classic falling rate of profit conditions. (2) 1984-1989 neo-liberal recovery — s/TV rose from 32% to 38%, driven by a 37% jump in the rate of surplus-value as Rogernomics reforms intensified labor exploitation. (3) 1990-1995 stagnation — s/TV plateaued at 38% despite continued rise in s/v, because renewed rise in value composition of capital offset gains in exploitation.</t>
+          <t>Annual s/TV values (decimal): 1972=0.34, 1973=0.36, 1974=0.34, 1975=0.29, 1976=0.30, 1977=0.33, 1978=0.31, 1979=0.32, 1980=0.32, 1981=0.32, 1982=0.31, 1983=0.31, 1984=0.32, 1985=0.32, 1986=0.34, 1987=0.37, 1988=0.37, 1989=0.38, 1990=0.38, 1991=0.38, 1992=0.38, 1993=0.37, 1994=0.38, 1995=0.38.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5; SUMMARY.md</t>
+          <t>Cronin_2001, Table 2; tables.csv</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>structural_break</t>
+          <t>periodization</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The 1984 Rogernomics reforms (Roger Douglas, Labour government) are the key structural break. Post-1984, the expansion of unproductive activity (financial sector, trade, administration) increased the unproductive share of gross output relative to total value — visible in gross output growing faster than total value from the late 1980s onward. The s/TV ratio improvement 1984-1989 masks the underlying dynamic: gains were exploitation-driven, not productivity-driven, and the unproductive sector drained surplus from productive investment.</t>
+          <t>Three distinct periods: (1) 1972-1983 profitability crisis — s/TV fell from 34% to 31%, reflecting a rising value composition of capital with stable exploitation rate; classic falling rate of profit conditions. (2) 1984-1989 neo-liberal recovery — s/TV rose from 32% to 38%, driven by a 37% jump in the rate of surplus-value as Rogernomics reforms intensified labor exploitation. (3) 1990-1995 stagnation — s/TV plateaued at 38% despite continued rise in s/v, because renewed rise in value composition of capital offset gains in exploitation.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
+          <t>Cronin_2001, body_text.md Section 5; SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>structural_break</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cronin Fig 10: plots s/TV for 1972-1995, showing the three-period structure. Fig 12: compares accumulation rate (s/TV) with rate of surplus-value (s/v), showing close tracking until the 1984-87 divergence when unproductive activity growth decoupled the two ratios.</t>
+          <t>The 1984 Rogernomics reforms (Roger Douglas, Labour government) are the key structural break. Post-1984, the expansion of unproductive activity (financial sector, trade, administration) increased the unproductive share of gross output relative to total value — visible in gross output growing faster than total value from the late 1980s onward. The s/TV ratio improvement 1984-1989 masks the underlying dynamic: gains were exploitation-driven, not productivity-driven, and the unproductive sector drained surplus from productive investment.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cronin_2001, body_text.md Section 5</t>
+          <t>Cronin_2001, body_text.md Section 5 (Growth of Unproductive Activity); SUMMARY.md</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cronin Fig 10: plots s/TV for 1972-1995, showing the three-period structure. Fig 12: compares accumulation rate (s/TV) with rate of surplus-value (s/v), showing close tracking until the 1984-87 divergence when unproductive activity growth decoupled the two ratios.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cronin_2001, body_text.md Section 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>caveat</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>s/TV is described by Cronin as the 'accumulation rate' — the share of total productive value available for accumulation. It differs from the conventional profit share because total value excludes unproductive activity. The conventional proxy (operating surplus / employee compensation) understates s/v by a factor of roughly 3-4 and shows little variation, while classical s/TV rises meaningfully from 1984.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Cronin_2001, body_text.md Section 4 (Conventional Proxy Measures); SUMMARY.md</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>s/TV (productive capital share / accumulation rate) is directly digitized from Cronin (2001) Table 2. Derived from NZSNA mapped to classical categories via Shaikh-Tonak methodology applied to 25 NZ production groups, 1972-1995. No extension beyond 1995.</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>No post-1995 extension available from this source</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1342,7 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Non-capitalist production (small self-employed and non-profit sector) assumed negligible and included as capitalist — Cronin notes data insufficient to isolate</t>
+          <t>No post-1995 extension available from this source</t>
         </is>
       </c>
     </row>
@@ -1341,23 +1350,23 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
+          <t>Non-capitalist production (small self-employed and non-profit sector) assumed negligible and included as capitalist — Cronin notes data insufficient to isolate</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Some inter-industry years interpolated using annual NZSNA data rather than full IO tables</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>cross_references:</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>XS1702</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1374,7 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XS1703</t>
+          <t>XS1702</t>
         </is>
       </c>
     </row>
@@ -1373,37 +1382,45 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
+          <t>XS1703</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>XS1704</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cronin_2001</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A mapping of the New Zealand system of national accounts to classical economic categories, 1972-95.' Review of Political Economy 13(3): 309-327. https://doi.org/10.1080/09538250120055168</t>
+          <t>citations:</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Cronin_2001</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cronin, Bruce. 2001. 'Productive and Unproductive Capital: A mapping of the New Zealand system of national accounts to classical economic categories, 1972-95.' Review of Political Economy 13(3): 309-327. https://doi.org/10.1080/09538250120055168</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
@@ -1504,7 +1521,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"1972": 0.34, "1989": 0.38, "1995": 0.38}</t>
+          <t>{"1972": 34, "1984": 32, "1989": 38, "1995": 38}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS1701.xlsx
+++ b/extenbooks/XS1701.xlsx
@@ -954,7 +954,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>`data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv` (copied from ST2's ExternalSources). Loader: `code/L01_loaders/L01_XS1701_nz_surplus_share_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1701_nz_surplus_share_cronin2001.py`.</t>
+          <t>`data/source/external_studies/Cronin2001_cronin_table2_ratios_1972_1995.csv` (copied from predecessor-build's ExternalSources). Loader: `code/L01_loaders/L01_XS1701_nz_surplus_share_cronin2001.py`. Processor: pass-through (P02). Validator: `code/V03_validators/V03_XS1701_nz_surplus_share_cronin2001.py`.</t>
         </is>
       </c>
     </row>
